--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,16 @@
           <t>Radius</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -450,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.69672</v>
+        <v>17.24958</v>
       </c>
       <c r="D2" t="n">
-        <v>16.90976</v>
+        <v>16.45149</v>
       </c>
       <c r="E2" t="n">
-        <v>17.05848</v>
+        <v>16.82944</v>
       </c>
       <c r="F2" t="n">
-        <v>43.01219</v>
+        <v>43.59942</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05131</v>
+        <v>0.05195</v>
       </c>
       <c r="H2" t="n">
-        <v>1.87732</v>
+        <v>1.88536</v>
       </c>
     </row>
     <row r="3">
@@ -475,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.10927</v>
+        <v>17.0989</v>
       </c>
       <c r="D3" t="n">
-        <v>16.57452</v>
+        <v>16.44522</v>
       </c>
       <c r="E3" t="n">
-        <v>16.98876</v>
+        <v>16.9066</v>
       </c>
       <c r="F3" t="n">
-        <v>43.4237</v>
+        <v>43.14363</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05043</v>
+        <v>0.05211</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84273</v>
+        <v>1.82391</v>
       </c>
     </row>
     <row r="4">
@@ -500,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.16402</v>
+        <v>17.30155</v>
       </c>
       <c r="D4" t="n">
-        <v>17.11285</v>
+        <v>17.03091</v>
       </c>
       <c r="E4" t="n">
-        <v>16.76106</v>
+        <v>17.23018</v>
       </c>
       <c r="F4" t="n">
-        <v>42.85027</v>
+        <v>42.42372</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05132</v>
+        <v>0.0517</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8443</v>
+        <v>1.8362</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.10096</v>
+        <v>16.98493</v>
       </c>
       <c r="D5" t="n">
-        <v>16.85137</v>
+        <v>16.31075</v>
       </c>
       <c r="E5" t="n">
-        <v>16.48175</v>
+        <v>16.87476</v>
       </c>
       <c r="F5" t="n">
-        <v>42.1335</v>
+        <v>42.56013</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05017</v>
+        <v>0.05091</v>
       </c>
       <c r="H5" t="n">
-        <v>1.87483</v>
+        <v>1.87827</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.2799</v>
+        <v>16.89895</v>
       </c>
       <c r="D6" t="n">
-        <v>17.01983</v>
+        <v>16.75034</v>
       </c>
       <c r="E6" t="n">
-        <v>16.55566</v>
+        <v>16.85931</v>
       </c>
       <c r="F6" t="n">
-        <v>42.4422</v>
+        <v>42.88571</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05141</v>
+        <v>0.05155</v>
       </c>
       <c r="H6" t="n">
-        <v>1.86776</v>
+        <v>1.89522</v>
       </c>
     </row>
     <row r="7">
@@ -575,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.02724</v>
+        <v>17.12182</v>
       </c>
       <c r="D7" t="n">
-        <v>16.65676</v>
+        <v>16.69269</v>
       </c>
       <c r="E7" t="n">
-        <v>16.40744</v>
+        <v>16.71545</v>
       </c>
       <c r="F7" t="n">
-        <v>43.28619</v>
+        <v>43.82979</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05035</v>
+        <v>0.05138</v>
       </c>
       <c r="H7" t="n">
-        <v>1.80543</v>
+        <v>1.86014</v>
       </c>
     </row>
     <row r="8">
@@ -600,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.06677</v>
+        <v>17.05848</v>
       </c>
       <c r="D8" t="n">
-        <v>16.70992</v>
+        <v>16.69672</v>
       </c>
       <c r="E8" t="n">
-        <v>16.67797</v>
+        <v>16.90976</v>
       </c>
       <c r="F8" t="n">
-        <v>42.91535</v>
+        <v>43.01219</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0517</v>
+        <v>0.05131</v>
       </c>
       <c r="H8" t="n">
-        <v>1.85965</v>
+        <v>1.87732</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.24832</v>
+        <v>17.10927</v>
       </c>
       <c r="D9" t="n">
-        <v>16.70028</v>
+        <v>16.57452</v>
       </c>
       <c r="E9" t="n">
-        <v>16.84201</v>
+        <v>16.98876</v>
       </c>
       <c r="F9" t="n">
-        <v>42.24701</v>
+        <v>43.4237</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05129</v>
+        <v>0.05043</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79948</v>
+        <v>1.84273</v>
       </c>
     </row>
     <row r="10">
@@ -650,31 +660,51 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.1786</v>
+        <v>17.16402</v>
       </c>
       <c r="D10" t="n">
-        <v>17.19236</v>
+        <v>16.76106</v>
       </c>
       <c r="E10" t="n">
-        <v>17.30491</v>
+        <v>17.11285</v>
       </c>
       <c r="F10" t="n">
-        <v>42.63324</v>
+        <v>42.85027</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05151</v>
+        <v>0.05132</v>
       </c>
       <c r="H10" t="n">
-        <v>1.80259</v>
+        <v>1.8443</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -688,14 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60844</v>
+        <v>17.10096</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13014</v>
+        <v>16.48175</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.85137</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.1335</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05017</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.87483</v>
       </c>
     </row>
     <row r="13">
@@ -705,10 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.61315</v>
+        <v>17.2799</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10975</v>
+        <v>16.55566</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.01983</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.4422</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05141</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.86776</v>
       </c>
     </row>
     <row r="14">
@@ -718,10 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.62146</v>
+        <v>17.02724</v>
       </c>
       <c r="D14" t="n">
-        <v>1.13515</v>
+        <v>16.40744</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.65676</v>
+      </c>
+      <c r="F14" t="n">
+        <v>43.28619</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05035</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.80543</v>
       </c>
     </row>
     <row r="15">
@@ -731,10 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6176199999999999</v>
+        <v>17.06677</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1126</v>
+        <v>16.67797</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.70992</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.91535</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.85965</v>
       </c>
     </row>
     <row r="16">
@@ -744,10 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60551</v>
+        <v>17.24832</v>
       </c>
       <c r="D16" t="n">
-        <v>1.14122</v>
+        <v>16.70028</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.84201</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.24701</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05129</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.79948</v>
       </c>
     </row>
     <row r="17">
@@ -757,10 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6192</v>
+        <v>17.30491</v>
       </c>
       <c r="D17" t="n">
-        <v>1.11663</v>
+        <v>17.1786</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.19236</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.63324</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05151</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.80259</v>
       </c>
     </row>
     <row r="18">
@@ -770,10 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.62754</v>
+        <v>16.86159</v>
       </c>
       <c r="D18" t="n">
-        <v>1.13545</v>
+        <v>16.83338</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.84937</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.37209</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05179</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.85752</v>
       </c>
     </row>
     <row r="19">
@@ -783,10 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6207</v>
+        <v>17.08749</v>
       </c>
       <c r="D19" t="n">
-        <v>1.11938</v>
+        <v>16.58781</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.65153</v>
+      </c>
+      <c r="F19" t="n">
+        <v>43.57372</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.82721</v>
       </c>
     </row>
     <row r="20">
@@ -796,51 +922,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6111799999999999</v>
+        <v>17.36203</v>
       </c>
       <c r="D20" t="n">
-        <v>1.13941</v>
+        <v>16.92846</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.06933</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.74004</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05093</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.86449</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -852,32 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.75217</v>
+        <v>15.84366</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0823</v>
+        <v>15.46395</v>
       </c>
       <c r="E22" t="n">
-        <v>0.60054</v>
+        <v>15.75499</v>
       </c>
       <c r="F22" t="n">
-        <v>0.97019</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.10951</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09382</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12901</v>
+        <v>256.74264</v>
       </c>
     </row>
     <row r="23">
@@ -887,28 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7770899999999999</v>
+        <v>16.21922</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08133</v>
+        <v>15.71673</v>
       </c>
       <c r="E23" t="n">
-        <v>0.61569</v>
+        <v>15.75556</v>
       </c>
       <c r="F23" t="n">
-        <v>0.96351</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.10888</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00765</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09357</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.13197</v>
+        <v>259.46387</v>
       </c>
     </row>
     <row r="24">
@@ -918,28 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7611599999999999</v>
+        <v>16.27692</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08255999999999999</v>
+        <v>15.65658</v>
       </c>
       <c r="E24" t="n">
-        <v>0.59567</v>
+        <v>15.85402</v>
       </c>
       <c r="F24" t="n">
-        <v>0.95545</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.10994</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00773</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09433999999999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12887</v>
+        <v>254.97471</v>
       </c>
     </row>
     <row r="25">
@@ -949,28 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.75768</v>
+        <v>15.71407</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08293</v>
+        <v>15.62591</v>
       </c>
       <c r="E25" t="n">
-        <v>0.62088</v>
+        <v>15.70918</v>
       </c>
       <c r="F25" t="n">
-        <v>0.97978</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.1114</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00769</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09402000000000001</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12971</v>
+        <v>265.41658</v>
       </c>
     </row>
     <row r="26">
@@ -980,28 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.75554</v>
+        <v>15.94326</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08196000000000001</v>
+        <v>15.33856</v>
       </c>
       <c r="E26" t="n">
-        <v>0.59682</v>
+        <v>15.89331</v>
       </c>
       <c r="F26" t="n">
-        <v>0.96621</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.10818</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0941</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12825</v>
+        <v>252.84227</v>
       </c>
     </row>
     <row r="27">
@@ -1011,28 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.74046</v>
+        <v>15.86258</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08185000000000001</v>
+        <v>15.77847</v>
       </c>
       <c r="E27" t="n">
-        <v>0.61273</v>
+        <v>15.84273</v>
       </c>
       <c r="F27" t="n">
-        <v>0.98647</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.11243</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00762</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09245</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.13057</v>
+        <v>259.18312</v>
       </c>
     </row>
     <row r="28">
@@ -1042,28 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.75696</v>
+        <v>15.98755</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08303000000000001</v>
+        <v>15.87027</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6095699999999999</v>
+        <v>15.96471</v>
       </c>
       <c r="F28" t="n">
-        <v>0.96961</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.11211</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09321</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12794</v>
+        <v>259.28162</v>
       </c>
     </row>
     <row r="29">
@@ -1073,28 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.76076</v>
+        <v>15.98773</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08194</v>
+        <v>15.78079</v>
       </c>
       <c r="E29" t="n">
-        <v>0.60906</v>
+        <v>15.78977</v>
       </c>
       <c r="F29" t="n">
-        <v>0.96357</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.11104</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09532</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12802</v>
+        <v>260.87006</v>
       </c>
     </row>
     <row r="30">
@@ -1104,28 +1126,1070 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.74597</v>
+        <v>15.8255</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08369</v>
+        <v>15.36802</v>
       </c>
       <c r="E30" t="n">
-        <v>0.62329</v>
+        <v>15.77803</v>
       </c>
       <c r="F30" t="n">
-        <v>0.99461</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.10919</v>
-      </c>
-      <c r="H30" t="n">
+        <v>255.68884</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.56963</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.25559</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.52805</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.05951</v>
+      </c>
+      <c r="G32" t="n">
+        <v>33.82081</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.88079</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.1352</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.82183</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.38109</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.35076</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.58066</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.50442</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.57138</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22.31401</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.33897</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.84067</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.40112</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.5811</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.78181</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.59526</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.96284</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.18318</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.44467</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.80722</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.75179</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.78638</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.36948</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.59114</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.67355</v>
+      </c>
+      <c r="G37" t="n">
+        <v>35.35799</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17.14044</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.37775</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.54201</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22.05646</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.55113</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>17.0938</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.0767</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.71794</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.51968</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.42784</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.03921</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.53476</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.58115</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.147</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.61572</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.90191</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.61007</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.61257</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.5671</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.23832</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.99194</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.02239</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.55367</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.15575</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.70802</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>17.07577</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.47966</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.53395</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22.09205</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.84488</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.76672</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.31868</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.62642</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.99121</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.93723</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.63945</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.20139</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.44031</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.60497</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.75539</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>17.12175</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.23345</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.61163</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.15338</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.94585</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.94043</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.1902</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.60887</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.95303</v>
+      </c>
+      <c r="G48" t="n">
+        <v>35.3454</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.82168</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.87027</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.38771</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.14594</v>
+      </c>
+      <c r="G49" t="n">
+        <v>35.54582</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.80144</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.3581</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.48524</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.19742</v>
+      </c>
+      <c r="G50" t="n">
+        <v>35.04323</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.62012</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.13979</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.60292</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.13086</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.6192299999999999</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.11687</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.62317</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.1374</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.60755</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.11052</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.61434</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.11002</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.61751</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.09385</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.61152</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.11339</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.60861</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.13679</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.61025</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.15371</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.62002</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.11577</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.62941</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.11782</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.61727</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.09994</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.60928</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.14589</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.60917</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.1451</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.62073</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.11661</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.6103</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.12159</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.61204</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.11963</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.75606</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08114</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6249</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.97583</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.1101</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.00773</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09401</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12853</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.75659</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08159</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.62029</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.96677</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.11232</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00772</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09544</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.12664</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.74771</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08193</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.60227</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.96394</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.11078</v>
+      </c>
+      <c r="H74" t="n">
         <v>0.00769</v>
       </c>
-      <c r="I30" t="n">
-        <v>0.09404</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.1295</v>
+      <c r="I74" t="n">
+        <v>0.09368</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.12875</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.74048</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08319</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.61443</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.99239</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.11265</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09313</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12923</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.75088</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08201</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.61077</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.95351</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.10961</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09594</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.12939</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.76494</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08314000000000001</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.61388</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.98537</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.10947</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09311</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.1278</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.76614</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08180999999999999</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.6122</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.97479</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.10964</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09406</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12883</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.75393</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.08118</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.62355</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.96479</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.11273</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00751</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09356</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.12688</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.75904</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08254</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.6277199999999999</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.95511</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.1107</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09421</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.12691</v>
       </c>
     </row>
   </sheetData>
